--- a/events/Gyor_2025_MAR/Gyor_2025_MAR_Results.xlsx
+++ b/events/Gyor_2025_MAR/Gyor_2025_MAR_Results.xlsx
@@ -57914,7 +57914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D476"/>
+  <dimension ref="A1:D475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61836,7 +61836,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>114225</t>
+          <t>147346</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -61858,61 +61858,61 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>147346</t>
+          <t>155249</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Chi Ham</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Hunter</t>
+          <t>Iao</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>155249</t>
+          <t>98874</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Chi Ham</t>
+          <t>Joaquin</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Iao</t>
+          <t>Iglesias Rodriguez</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>98874</t>
+          <t>159906</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Joaquin</t>
+          <t>Qing Hao Salman</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Iglesias Rodriguez</t>
+          <t>Irfan Putera</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -61924,17 +61924,17 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>159906</t>
+          <t>113405</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Qing Hao Salman</t>
+          <t>Sota</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Irfan Putera</t>
+          <t>Iwai</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -61946,17 +61946,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>113405</t>
+          <t>155114</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Sota</t>
+          <t>Beau</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Iwai</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -61968,12 +61968,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>155114</t>
+          <t>141598</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Beau</t>
+          <t>Connor</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -61990,17 +61990,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>141598</t>
+          <t>113503</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Connor</t>
+          <t>Filip</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Jahoda</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -62012,61 +62012,61 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>113503</t>
+          <t>148851</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Filip</t>
+          <t>Lotti</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Jahoda</t>
+          <t>Jambor</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>148851</t>
+          <t>128610</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Lotti</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Jambor</t>
+          <t>Jenkin</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>128610</t>
+          <t>102569</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Isaac</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Jenkin</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -62078,12 +62078,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>102569</t>
+          <t>85376</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Isaac</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -62100,61 +62100,61 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>85376</t>
+          <t>122322</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Leona</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Johs</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>122322</t>
+          <t>160033</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Leona</t>
+          <t>Francois</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Johs</t>
+          <t>Jonquet</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>160033</t>
+          <t>113662</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Francois</t>
+          <t>Valdemar</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Jonquet</t>
+          <t>Jorgensen</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -62166,17 +62166,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>113662</t>
+          <t>88869</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Valdemar</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Jorgensen</t>
+          <t>Karakolev</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -62188,39 +62188,39 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>88869</t>
+          <t>156649</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Valeriia</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Karakolev</t>
+          <t>Kashubina</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>156649</t>
+          <t>156095</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Valeriia</t>
+          <t>Reka Sara</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Kashubina</t>
+          <t>Katona</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -62232,105 +62232,105 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>156095</t>
+          <t>146995</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Reka Sara</t>
+          <t>Mahiro</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Katona</t>
+          <t>Kawagoe</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>146995</t>
+          <t>161555</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Mahiro</t>
+          <t>Isabella</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Kawagoe</t>
+          <t>Keane</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>161555</t>
+          <t>130229</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Gabin</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Keane</t>
+          <t>Keirel</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>130229</t>
+          <t>127578</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Gabin</t>
+          <t>Doreen</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Keirel</t>
+          <t>Kemp</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>127578</t>
+          <t>162141</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Doreen</t>
+          <t>Mariia</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Kemp</t>
+          <t>Kharitonova</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -62342,78 +62342,78 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>162141</t>
+          <t>49274</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Mariia</t>
+          <t>Joshua</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Kharitonova</t>
+          <t>Kippin</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>49274</t>
+          <t>63478</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Joshua</t>
+          <t>Zsofia Nora</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Kippin</t>
+          <t>Kisban</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>63478</t>
+          <t>75635</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Zsofia Nora</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Kisban</t>
+          <t>Kiss</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>75635</t>
+          <t>94068</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -62430,12 +62430,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>94068</t>
+          <t>134603</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Tibor</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -62452,61 +62452,61 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>134603</t>
+          <t>49657</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Tibor</t>
+          <t>Vanda</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Kiss</t>
+          <t>Kiszli</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>49657</t>
+          <t>137975</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Vanda</t>
+          <t>Michal</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Kiszli</t>
+          <t>Klima</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>137975</t>
+          <t>95939</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Michal</t>
+          <t>Philip</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Klima</t>
+          <t>Knudsen</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -62518,39 +62518,39 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>95939</t>
+          <t>137795</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Philip</t>
+          <t>Tereza</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Knudsen</t>
+          <t>Kodetova</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>137795</t>
+          <t>104824</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Tereza</t>
+          <t>Lillemor</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Kodetova</t>
+          <t>Koeper</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -62562,78 +62562,78 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>104824</t>
+          <t>135712</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Lillemor</t>
+          <t>Mate</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Koeper</t>
+          <t>Kollek</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>135712</t>
+          <t>149420</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Mate</t>
+          <t>Irina</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Kollek</t>
+          <t>Kolobova</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>149420</t>
+          <t>105015</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Irina</t>
+          <t>Bruno</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Kolobova</t>
+          <t>Kolozsvari</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>105015</t>
+          <t>161062</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Bruno</t>
+          <t>Lili</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -62643,24 +62643,24 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>161062</t>
+          <t>138846</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Lili</t>
+          <t>Liv-Grete</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Kolozsvari</t>
+          <t>Kontopp</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -62672,39 +62672,39 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>138846</t>
+          <t>137812</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Liv-Grete</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Kontopp</t>
+          <t>Koula</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>137812</t>
+          <t>161885</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Rustam</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Koula</t>
+          <t>Kovalenko</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -62716,17 +62716,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>161885</t>
+          <t>156653</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Rustam</t>
+          <t>Aleksandr</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Kovalenko</t>
+          <t>Kovalev</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -62738,39 +62738,39 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>156653</t>
+          <t>138049</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Aleksandr</t>
+          <t>Agata</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Kovalev</t>
+          <t>Kowalak</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>138049</t>
+          <t>80348</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Agata</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Kowalak</t>
+          <t>Kozikowska</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -62782,17 +62782,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>80348</t>
+          <t>147279</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Anastasiia</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Kozikowska</t>
+          <t>Kravchenko</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -62804,17 +62804,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>147279</t>
+          <t>130981</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Anastasiia</t>
+          <t>Brynde</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Kravchenko</t>
+          <t>Kreft</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -62826,17 +62826,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>130981</t>
+          <t>157628</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Brynde</t>
+          <t>Alayah</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Kreft</t>
+          <t>Krogscheepers</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -62848,17 +62848,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>157628</t>
+          <t>130427</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Alayah</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Krogscheepers</t>
+          <t>Kukla</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -62870,39 +62870,39 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>130427</t>
+          <t>161692</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Kukla</t>
+          <t>Kunc</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>161692</t>
+          <t>158991</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Jakub</t>
+          <t>Ryota</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Kunc</t>
+          <t>Kusakawa</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -62914,17 +62914,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>158991</t>
+          <t>161884</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Ryota</t>
+          <t>Mykola</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Kusakawa</t>
+          <t>Kuzminets</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -62936,17 +62936,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>161884</t>
+          <t>146818</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Mykola</t>
+          <t>Antonis</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Kuzminets</t>
+          <t>Kyriacou</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -62958,17 +62958,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>146818</t>
+          <t>48163</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Antonis</t>
+          <t>Rui</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Kyriacou</t>
+          <t>Lacerda</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -62980,17 +62980,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>48163</t>
+          <t>58736</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Rui</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Lacerda</t>
+          <t>Laczo</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -63002,17 +63002,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>58736</t>
+          <t>148293</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Zarand Janos</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Laczo</t>
+          <t>Lanczi</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -63024,83 +63024,83 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>148293</t>
+          <t>161536</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Zarand Janos</t>
+          <t>Aino-Linnea</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Lanczi</t>
+          <t>Lantelankallio</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>161536</t>
+          <t>160457</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Aino-Linnea</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Lantelankallio</t>
+          <t>Lanzon</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>160457</t>
+          <t>61312</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Agnes</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Lanzon</t>
+          <t>Legroux</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>61312</t>
+          <t>161974</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Agnes</t>
+          <t>Pui U</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Legroux</t>
+          <t>Lei</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -63112,105 +63112,105 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>161974</t>
+          <t>160454</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Pui U</t>
+          <t>Yuri Francisco</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Lei</t>
+          <t>Leiva</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>160454</t>
+          <t>147832</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Yuri Francisco</t>
+          <t>Kai Jing</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Leiva</t>
+          <t>Lim</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>147832</t>
+          <t>52099</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Kai Jing</t>
+          <t>Joakim</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Lim</t>
+          <t>Lindberg</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>52099</t>
+          <t>146311</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Joakim</t>
+          <t>Anna Hilda</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Lindberg</t>
+          <t>Lindeberg</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>146311</t>
+          <t>138833</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Anna Hilda</t>
+          <t>Lotte Luise</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Lindeberg</t>
+          <t>Liwowski</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -63222,39 +63222,39 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>138833</t>
+          <t>61361</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Lotte Luise</t>
+          <t>Timothy</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Liwowski</t>
+          <t>Lodge</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>61361</t>
+          <t>75690</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Timothy</t>
+          <t>Javier</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Lodge</t>
+          <t>Lopez Gonzalez</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -63266,17 +63266,17 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>75690</t>
+          <t>69017</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Javier</t>
+          <t>Milton</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Lopez Gonzalez</t>
+          <t>Luz De Oliveira</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -63288,17 +63288,17 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>69017</t>
+          <t>115170</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Milton</t>
+          <t>Yehor</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Luz De Oliveira</t>
+          <t>Lyshchuk</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -63310,83 +63310,83 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>115170</t>
+          <t>144683</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Yehor</t>
+          <t>Daria</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Lyshchuk</t>
+          <t>Macan</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>144683</t>
+          <t>160194</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Daria</t>
+          <t>Hunter</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Macan</t>
+          <t>Mack</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>160194</t>
+          <t>85181</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Hunter</t>
+          <t>Martina</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Mack</t>
+          <t>Malikova</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>85181</t>
+          <t>155122</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Martina</t>
+          <t>Kathy</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Malikova</t>
+          <t>Mallory</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -63398,17 +63398,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>155122</t>
+          <t>136712</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Kathy</t>
+          <t>Lilou</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Mallory</t>
+          <t>Mangot</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -63420,17 +63420,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>136712</t>
+          <t>64233</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Lilou</t>
+          <t>Rebecca</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Mangot</t>
+          <t>Mann</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -63442,56 +63442,56 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>64233</t>
+          <t>98395</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Rebecca</t>
+          <t>Soren</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Mann</t>
+          <t>Maretti</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>98395</t>
+          <t>49278</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Soren</t>
+          <t>Bronwyn</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Maretti</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>49278</t>
+          <t>71701</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Bronwyn</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -63508,39 +63508,39 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>71701</t>
+          <t>134141</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Martinez</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>134141</t>
+          <t>155049</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Dario</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Martinez</t>
+          <t>Martinez Hernandez</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -63552,39 +63552,39 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>155049</t>
+          <t>105061</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Dario</t>
+          <t>Lili Sara</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Martinez Hernandez</t>
+          <t>Matkovics</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>105061</t>
+          <t>143938</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Lili Sara</t>
+          <t>Nikol</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Matkovics</t>
+          <t>Matnenko</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -63596,17 +63596,17 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>143938</t>
+          <t>160426</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Nikol</t>
+          <t>Anetta Nikoletta</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Matnenko</t>
+          <t>Mazug</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -63618,34 +63618,34 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>160426</t>
+          <t>48400</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Anetta Nikoletta</t>
+          <t>Hank</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Mazug</t>
+          <t>Mcgregor</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>48400</t>
+          <t>122402</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Hank</t>
+          <t>Pippa</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -63655,46 +63655,46 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>122402</t>
+          <t>132588</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Pippa</t>
+          <t>Lukas</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Mcgregor</t>
+          <t>Meemann</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>132588</t>
+          <t>105770</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Lukas</t>
+          <t>Tristan</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Meemann</t>
+          <t>Meersmans</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -63706,105 +63706,105 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>105770</t>
+          <t>128733</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Tristan</t>
+          <t>Araceli</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Meersmans</t>
+          <t>Menduina</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>128733</t>
+          <t>114166</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Araceli</t>
+          <t>Cartouche</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Menduina</t>
+          <t>Mensink</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>114166</t>
+          <t>137933</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Cartouche</t>
+          <t>Nela</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Mensink</t>
+          <t>Meszarosova</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>137933</t>
+          <t>123343</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Nela</t>
+          <t>Diego</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Meszarosova</t>
+          <t>Miguens</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>123343</t>
+          <t>161989</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Diego</t>
+          <t>Alexandre</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Miguens</t>
+          <t>Miguez</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -63816,56 +63816,56 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>161989</t>
+          <t>76971</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Alexandre</t>
+          <t>Katerina</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Miguez</t>
+          <t>Milova</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>76971</t>
+          <t>161064</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Katerina</t>
+          <t>Merse</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Milova</t>
+          <t>Molnar</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>161064</t>
+          <t>94067</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Merse</t>
+          <t>Nikoletta</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -63875,68 +63875,68 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>94067</t>
+          <t>160197</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Nikoletta</t>
+          <t>Konrad</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Molnar</t>
+          <t>Morawski</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>160197</t>
+          <t>53551</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Konrad</t>
+          <t>Wakana</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Morawski</t>
+          <t>Moriyama</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>53551</t>
+          <t>147320</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Wakana</t>
+          <t>Alexandra</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Moriyama</t>
+          <t>Motovska</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -63948,83 +63948,83 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>147320</t>
+          <t>148799</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Alexandra</t>
+          <t>Andras</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Motovska</t>
+          <t>Mozes</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>148799</t>
+          <t>146569</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Andras</t>
+          <t>Maya</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Mozes</t>
+          <t>Murphy</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>146569</t>
+          <t>135293</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Maya</t>
+          <t>Gergely</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Murphy</t>
+          <t>Nagy</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>135293</t>
+          <t>148292</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Gergely</t>
+          <t>Vince</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Nagy</t>
+          <t>Nagy-Rasztotzky</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -64036,39 +64036,39 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>148292</t>
+          <t>146999</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Vince</t>
+          <t>Nodoka</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Nagy-Rasztotzky</t>
+          <t>Nakahara</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>146999</t>
+          <t>153677</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Nodoka</t>
+          <t>Florence Prossy</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Nakahara</t>
+          <t>Namanda</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -64080,39 +64080,39 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>153677</t>
+          <t>47634</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Florence Prossy</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Namanda</t>
+          <t>Nathell</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>47634</t>
+          <t>160152</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Zakhar</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Nathell</t>
+          <t>Nazarenko</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -64124,17 +64124,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>160152</t>
+          <t>156630</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Zakhar</t>
+          <t>Ivan</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Nazarenko</t>
+          <t>Nekrasov</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -64146,34 +64146,34 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>156630</t>
+          <t>147775</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Ivan</t>
+          <t>Hana</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Nekrasov</t>
+          <t>Newlands</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>147775</t>
+          <t>63896</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Hana</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -64183,24 +64183,24 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>63896</t>
+          <t>94101</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Mirko</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Newlands</t>
+          <t>Nicoli</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -64212,61 +64212,61 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>94101</t>
+          <t>115024</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Mirko</t>
+          <t>Agnete</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Nicoli</t>
+          <t>Nielsen</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>115024</t>
+          <t>145018</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Agnete</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Nielsen</t>
+          <t>Nijakowski</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>145018</t>
+          <t>135160</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Lars</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Nijakowski</t>
+          <t>Nikolay</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -64278,61 +64278,61 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>135160</t>
+          <t>48413</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Lars</t>
+          <t>Jenna</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Nikolay</t>
+          <t>Nisbet</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>48413</t>
+          <t>146339</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Jenna</t>
+          <t>Rikuto</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Nisbet</t>
+          <t>Noda</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>146339</t>
+          <t>49662</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Rikuto</t>
+          <t>Balint</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Noda</t>
+          <t>Noe</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -64344,105 +64344,105 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>49662</t>
+          <t>147776</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Balint</t>
+          <t>Tayla</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Noe</t>
+          <t>Norton</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>147776</t>
+          <t>48415</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Tayla</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Norton</t>
+          <t>Notten</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>48415</t>
+          <t>160232</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Zakaria Abakar</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Notten</t>
+          <t>Nouracham</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>160232</t>
+          <t>137799</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Zakaria Abakar</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Nouracham</t>
+          <t>Novacek</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>137799</t>
+          <t>161688</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Riccardo</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Novacek</t>
+          <t>Novella</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -64454,105 +64454,105 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>161688</t>
+          <t>128723</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Riccardo</t>
+          <t>Nerea</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Novella</t>
+          <t>Novo</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>128723</t>
+          <t>136358</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Nerea</t>
+          <t>Timo Alexander</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Novo</t>
+          <t>Nowak Lonsdale</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>136409</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Timo Alexander</t>
+          <t>Ana-Lucia</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Nowak Lonsdale</t>
+          <t>Nowakowski</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>136409</t>
+          <t>121683</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Ana-Lucia</t>
+          <t>Miska</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Nowakowski</t>
+          <t>Nummela</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>121683</t>
+          <t>118712</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Miska</t>
+          <t>Oleg</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Nummela</t>
+          <t>Nuta</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -64564,39 +64564,39 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>118712</t>
+          <t>158987</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Oleg</t>
+          <t>Akari</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Nuta</t>
+          <t>Okino</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>158987</t>
+          <t>75588</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Akari</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Okino</t>
+          <t>Olarasu</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -64608,17 +64608,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>75588</t>
+          <t>136869</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Hannah Shu En</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Olarasu</t>
+          <t>Ong</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -64630,39 +64630,39 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>136869</t>
+          <t>162108</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Hannah Shu En</t>
+          <t>Oleksandr</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Ong</t>
+          <t>Onishchenko</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>162108</t>
+          <t>158985</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Oleksandr</t>
+          <t>Kai</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Onishchenko</t>
+          <t>Ono</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -64674,17 +64674,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>158985</t>
+          <t>159903</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Kai</t>
+          <t>Yong En Colin</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Ono</t>
+          <t>Ooi</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -64696,17 +64696,17 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>159903</t>
+          <t>154276</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Yong En Colin</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Ooi</t>
+          <t>Ordonez-Martinez</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -64718,61 +64718,61 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>154276</t>
+          <t>57986</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Irati</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Ordonez-Martinez</t>
+          <t>Osa Irureta</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>57986</t>
+          <t>159077</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Irati</t>
+          <t>Rei</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Osa Irureta</t>
+          <t>Otani</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>159077</t>
+          <t>46806</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Rei</t>
+          <t>Roberto Carlos</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Otani</t>
+          <t>Palacios</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -64784,17 +64784,17 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>46806</t>
+          <t>38994</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Roberto Carlos</t>
+          <t>Marcel</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Palacios</t>
+          <t>Paufler</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -64806,12 +64806,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>38994</t>
+          <t>63457</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Marcel</t>
+          <t>Nico</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -64828,12 +64828,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>63457</t>
+          <t>49777</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Nico</t>
+          <t>Sven</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -64850,17 +64850,17 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>49777</t>
+          <t>49618</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Sven</t>
+          <t>Mads Brandt</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Paufler</t>
+          <t>Pedersen</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -64872,17 +64872,17 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>49618</t>
+          <t>117495</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Mads Brandt</t>
+          <t>Zalan</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Pedersen</t>
+          <t>Peli</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -64894,17 +64894,17 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>117495</t>
+          <t>149470</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Zalan</t>
+          <t>Jorge</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Peli</t>
+          <t>Perez</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -64916,17 +64916,17 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>149470</t>
+          <t>162104</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Jorge</t>
+          <t>Pablo</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Perez</t>
+          <t>Perez Alvarez</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -64938,61 +64938,61 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>162104</t>
+          <t>114368</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Pablo</t>
+          <t>Johanna</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Perez Alvarez</t>
+          <t>Pfluegner</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>114368</t>
+          <t>160233</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Johanna</t>
+          <t>Cristian</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Pfluegner</t>
+          <t>Piazza</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>160233</t>
+          <t>36448</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Cristian</t>
+          <t>Fernando</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Piazza</t>
+          <t>Pimenta</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -65004,17 +65004,17 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>36448</t>
+          <t>160406</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Jose Javier</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Pimenta</t>
+          <t>Pineiro</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -65026,105 +65026,105 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>160406</t>
+          <t>155058</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Jose Javier</t>
+          <t>Lucia</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Pineiro</t>
+          <t>Pizarro Dorado</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>155058</t>
+          <t>104820</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Lucia</t>
+          <t>Mihaly</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Pizarro Dorado</t>
+          <t>Pluzsik</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>104820</t>
+          <t>161882</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Mihaly</t>
+          <t>Oleksandra</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Pluzsik</t>
+          <t>Polezhaieva</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>161882</t>
+          <t>132970</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Oleksandra</t>
+          <t>Maik</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Polezhaieva</t>
+          <t>Polte</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>132970</t>
+          <t>112331</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Maik</t>
+          <t>Adrian</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Polte</t>
+          <t>Prada Perez</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -65136,61 +65136,61 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>112331</t>
+          <t>157644</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Adrian</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Prada Perez</t>
+          <t>Privett</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>157644</t>
+          <t>161881</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Vadym</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Privett</t>
+          <t>Prokopets</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>161881</t>
+          <t>155719</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Vadym</t>
+          <t>Franck</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Prokopets</t>
+          <t>Prud'homme</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -65202,17 +65202,17 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>155719</t>
+          <t>136590</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Franck</t>
+          <t>Jonathan Legart</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Prud'homme</t>
+          <t>Qvist</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -65224,61 +65224,61 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>136590</t>
+          <t>160107</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Jonathan Legart</t>
+          <t>Willemijn</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Qvist</t>
+          <t>Raaijmaakers</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>160107</t>
+          <t>155050</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Willemijn</t>
+          <t>Jaime</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Raaijmaakers</t>
+          <t>Rainero</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>155050</t>
+          <t>94174</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Jaime</t>
+          <t>Mukhammadi</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Rainero</t>
+          <t>Rajabov</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -65290,17 +65290,17 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>94174</t>
+          <t>48161</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Mukhammadi</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Rajabov</t>
+          <t>Ramalho</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -65312,17 +65312,17 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>48161</t>
+          <t>76507</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Thorbjorn</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Ramalho</t>
+          <t>Rask</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -65334,17 +65334,17 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>76507</t>
+          <t>133000</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Thorbjorn</t>
+          <t>Pedro Agustin</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Rask</t>
+          <t>Ratto</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -65356,17 +65356,17 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>87558</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Pedro Agustin</t>
+          <t>Maksym</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Ratto</t>
+          <t>Redko</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -65378,39 +65378,39 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>87558</t>
+          <t>98603</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Maksym</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Redko</t>
+          <t>Rego Gomes</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>98603</t>
+          <t>108068</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Justyna</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Rego Gomes</t>
+          <t>Regucka</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -65422,17 +65422,17 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>108068</t>
+          <t>133328</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Janka</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Regucka</t>
+          <t>Reisz</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -65444,61 +65444,61 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>133328</t>
+          <t>46847</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Janka</t>
+          <t>Javier</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Reisz</t>
+          <t>Reja</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>46847</t>
+          <t>112905</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Javier</t>
+          <t>Ella</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Reja</t>
+          <t>Richter</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>112905</t>
+          <t>57968</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Ella</t>
+          <t>Nina</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Richter</t>
+          <t>Riosa</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -65510,61 +65510,61 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>57968</t>
+          <t>160191</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Nina</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Riosa</t>
+          <t>Robichaud</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>160191</t>
+          <t>143156</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Robichaud</t>
+          <t>Roche</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>143156</t>
+          <t>112334</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Roche</t>
+          <t>Rodriguez Alonso</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -65576,39 +65576,39 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>112334</t>
+          <t>161538</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>William</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Rodriguez Alonso</t>
+          <t>Roeser</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>161538</t>
+          <t>160196</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Charlie</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Roeser</t>
+          <t>Rogers</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -65620,17 +65620,17 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>160196</t>
+          <t>149464</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Charlie</t>
+          <t>Alberto</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Rogers</t>
+          <t>Ruiz</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -65642,17 +65642,17 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>149464</t>
+          <t>53158</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Alberto</t>
+          <t>James</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Ruiz</t>
+          <t>Russell</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -65664,17 +65664,17 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>53158</t>
+          <t>160449</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Leonel Alessandro</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Russell</t>
+          <t>Russo</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -65686,61 +65686,61 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>160449</t>
+          <t>138037</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Leonel Alessandro</t>
+          <t>Zuzanna</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Russo</t>
+          <t>Rynkiewicz</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>138037</t>
+          <t>161880</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Zuzanna</t>
+          <t>Vladyslav</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Rynkiewicz</t>
+          <t>Sadovnykov</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>161880</t>
+          <t>122389</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Vladyslav</t>
+          <t>Syver</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Sadovnykov</t>
+          <t>Saksvik</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -65752,17 +65752,17 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>122389</t>
+          <t>116918</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Syver</t>
+          <t>Julian Daniel</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Saksvik</t>
+          <t>Salinas</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -65774,17 +65774,17 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>116918</t>
+          <t>128721</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Julian Daniel</t>
+          <t>Dario</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Salinas</t>
+          <t>Sanchez</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -65796,17 +65796,17 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>128721</t>
+          <t>162146</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Dario</t>
+          <t>Alarik</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Sanchez</t>
+          <t>Sandrup</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -65818,61 +65818,61 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>162146</t>
+          <t>155055</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Alarik</t>
+          <t>Danae</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Sandrup</t>
+          <t>Sanmartin</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>155055</t>
+          <t>147523</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Danae</t>
+          <t>Davide</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Sanmartin</t>
+          <t>Sartori</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>147523</t>
+          <t>158988</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Davide</t>
+          <t>Kiminori</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Sartori</t>
+          <t>Sato</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -65884,105 +65884,105 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>158988</t>
+          <t>160452</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Kiminori</t>
+          <t>Juliana</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Sato</t>
+          <t>Saunders</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>160452</t>
+          <t>160193</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Juliana</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Saunders</t>
+          <t>Schlosser</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>160193</t>
+          <t>160458</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Jazmin</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Schlosser</t>
+          <t>Schneider</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>160458</t>
+          <t>161203</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Jazmin</t>
+          <t>Johannes</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Schneider</t>
+          <t>Schwenzer</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>161203</t>
+          <t>104881</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Johannes</t>
+          <t>Csanad</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Schwenzer</t>
+          <t>Sellyei</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -65994,61 +65994,61 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>104881</t>
+          <t>161878</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Csanad</t>
+          <t>Viktoriia</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Sellyei</t>
+          <t>Semerak</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>161878</t>
+          <t>161879</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Viktoriia</t>
+          <t>Bohdan</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Semerak</t>
+          <t>Sezko</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>161879</t>
+          <t>79760</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Bohdan</t>
+          <t>Ajatsatru</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Sezko</t>
+          <t>Sharma</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -66060,17 +66060,17 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>79760</t>
+          <t>160423</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Ajatsatru</t>
+          <t>Stone</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Sharma</t>
+          <t>Shearer</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -66082,17 +66082,17 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>160423</t>
+          <t>46397</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Stone</t>
+          <t>Eduard</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Shearer</t>
+          <t>Shemetylo</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -66104,17 +66104,17 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>46397</t>
+          <t>135253</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Eduard</t>
+          <t>William</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Shemetylo</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -66126,17 +66126,17 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>135253</t>
+          <t>134249</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Jared</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Short</t>
+          <t>Shrimpton</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -66148,17 +66148,17 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>134249</t>
+          <t>149468</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Jared</t>
+          <t>Jaser Antonio</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Shrimpton</t>
+          <t>Silva</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -66170,17 +66170,17 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>149468</t>
+          <t>137803</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Jaser Antonio</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Silva</t>
+          <t>Sindel</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -66192,39 +66192,39 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>137803</t>
+          <t>94211</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Jakub</t>
+          <t>Panna</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Sindel</t>
+          <t>Sinko</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>94211</t>
+          <t>155773</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Panna</t>
+          <t>Neele</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Sinko</t>
+          <t>Skibbe</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -66236,17 +66236,17 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>155773</t>
+          <t>158595</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Neele</t>
+          <t>Judit</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Skibbe</t>
+          <t>Sklanicz</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -66258,17 +66258,17 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>158595</t>
+          <t>121751</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Judit</t>
+          <t>Kamila</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Sklanicz</t>
+          <t>Sklenarova</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -66280,17 +66280,17 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>121751</t>
+          <t>72810</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Kamila</t>
+          <t>Olena</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Sklenarova</t>
+          <t>Skvortsova</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -66302,17 +66302,17 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>72810</t>
+          <t>53544</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Olena</t>
+          <t>Anna Margrete</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Skvortsova</t>
+          <t>Sletsjoee</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -66324,39 +66324,39 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>53544</t>
+          <t>155940</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Anna Margrete</t>
+          <t>Ribe</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Sletsjoee</t>
+          <t>Smids</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>155940</t>
+          <t>64942</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Ribe</t>
+          <t>Charles</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Smids</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -66368,12 +66368,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>64942</t>
+          <t>134250</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>Ryley</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -66390,17 +66390,17 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>134250</t>
+          <t>131144</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Ryley</t>
+          <t>Sean</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Smyth</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -66412,17 +66412,17 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>131144</t>
+          <t>135754</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Sean</t>
+          <t>Mihails</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Smyth</t>
+          <t>Solovejs</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -66434,17 +66434,17 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>135754</t>
+          <t>114632</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Mihails</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Solovejs</t>
+          <t>Soltesz</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -66456,17 +66456,17 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>114632</t>
+          <t>132977</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Frederik Dziegiel</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Soltesz</t>
+          <t>Sondergaard</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -66478,17 +66478,17 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>132977</t>
+          <t>133093</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Frederik Dziegiel</t>
+          <t>Joao</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Sondergaard</t>
+          <t>Sousa</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -66500,17 +66500,17 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>133093</t>
+          <t>149065</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Joao</t>
+          <t>Rafael</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Sousa</t>
+          <t>Sousa Da Conceicao</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -66522,17 +66522,17 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>149065</t>
+          <t>130418</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Rafael</t>
+          <t>Ilie</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Sousa Da Conceicao</t>
+          <t>Sprincean</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -66544,17 +66544,17 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>130418</t>
+          <t>75788</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Ilie</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Sprincean</t>
+          <t>St-Pierre</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -66566,17 +66566,17 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>75788</t>
+          <t>134186</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Cody</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>St-Pierre</t>
+          <t>Stallard</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -66588,17 +66588,17 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>134186</t>
+          <t>145017</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Cody</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Stallard</t>
+          <t>Stanio</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -66610,83 +66610,83 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>145017</t>
+          <t>128298</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Genevieve</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Stanio</t>
+          <t>Stanley</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>128298</t>
+          <t>133069</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Genevieve</t>
+          <t>Patryk</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Stanley</t>
+          <t>Stasielowicz</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>133069</t>
+          <t>146313</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Patryk</t>
+          <t>Rut</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Stasielowicz</t>
+          <t>Stening</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>146313</t>
+          <t>136812</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Rut</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Stening</t>
+          <t>Stoubaek Andersen</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -66698,17 +66698,17 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>136812</t>
+          <t>157641</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Isabella</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Stoubaek Andersen</t>
+          <t>Strydom</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -66720,127 +66720,127 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>157641</t>
+          <t>56181</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Strydom</t>
+          <t>Suba</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>56181</t>
+          <t>114733</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Romana</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Suba</t>
+          <t>Svecova</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>114733</t>
+          <t>36427</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Romana</t>
+          <t>Markus Mendy</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Svecova</t>
+          <t>Swoboda</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>36427</t>
+          <t>104759</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Markus Mendy</t>
+          <t>Zsofia</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Swoboda</t>
+          <t>Szerafin</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>104759</t>
+          <t>160380</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Zsofia</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Szerafin</t>
+          <t>Szpak</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>160380</t>
+          <t>112804</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Jakub</t>
+          <t>Alexandru</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Szpak</t>
+          <t>Tacu</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -66852,17 +66852,17 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>112804</t>
+          <t>158984</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Alexandru</t>
+          <t>Keisuke</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Tacu</t>
+          <t>Takahashi</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -66874,17 +66874,17 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>158984</t>
+          <t>103499</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Keisuke</t>
+          <t>Issei</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Takahashi</t>
+          <t>Takenaka</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -66896,61 +66896,61 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>103499</t>
+          <t>162147</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Issei</t>
+          <t>Alessandra</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Takenaka</t>
+          <t>Talita Teixeira Gomes</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>162147</t>
+          <t>159905</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Alessandra</t>
+          <t>Julian</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Talita Teixeira Gomes</t>
+          <t>Tan</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>159905</t>
+          <t>142023</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Julian</t>
+          <t>Lik Tin</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Tan</t>
+          <t>Tang</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -66962,17 +66962,17 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>142023</t>
+          <t>53071</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Lik Tin</t>
+          <t>Oleg</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Tang</t>
+          <t>Tarnovschi</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -66984,12 +66984,12 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>53071</t>
+          <t>53072</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Oleg</t>
+          <t>Serghei</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -67006,17 +67006,17 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>53072</t>
+          <t>126897</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Serghei</t>
+          <t>Rakshit</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Tarnovschi</t>
+          <t>Tashir</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -67028,61 +67028,61 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>126897</t>
+          <t>141881</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Rakshit</t>
+          <t>Sophie</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Tashir</t>
+          <t>Tasker</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>141881</t>
+          <t>104722</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Sophie</t>
+          <t>Rik</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Tasker</t>
+          <t>Te Linde</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>104722</t>
+          <t>160424</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Rik</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Te Linde</t>
+          <t>Tobin</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -67094,17 +67094,17 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>160424</t>
+          <t>118544</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Aryan</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Tobin</t>
+          <t>Tomar</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -67116,17 +67116,17 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>118544</t>
+          <t>154326</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Aryan</t>
+          <t>Clement</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Tomar</t>
+          <t>Touchaud</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -67138,17 +67138,17 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>154326</t>
+          <t>160450</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Clement</t>
+          <t>Eitan</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Touchaud</t>
+          <t>Trajtman</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -67160,105 +67160,105 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>160450</t>
+          <t>160192</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Eitan</t>
+          <t>Lyne</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Trajtman</t>
+          <t>Tremblay</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>160192</t>
+          <t>156879</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Lyne</t>
+          <t>Dmitrii</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Tremblay</t>
+          <t>Trubin</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>156879</t>
+          <t>79100</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Dmitrii</t>
+          <t>Olena</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Trubin</t>
+          <t>Tsyhankova</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>79100</t>
+          <t>160189</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Olena</t>
+          <t>Julien</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Tsyhankova</t>
+          <t>Turpin</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>160189</t>
+          <t>158990</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Julien</t>
+          <t>Shitora</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Turpin</t>
+          <t>Uede</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -67270,17 +67270,17 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>158990</t>
+          <t>104757</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Shitora</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Uede</t>
+          <t>Uhrin</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -67292,61 +67292,61 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>104757</t>
+          <t>133015</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Uhrin</t>
+          <t>Urquhart</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>133015</t>
+          <t>147865</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Facundo</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Urquhart</t>
+          <t>Valenzuela</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>147865</t>
+          <t>143639</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Facundo</t>
+          <t>Sander</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Valenzuela</t>
+          <t>Van Uytvanck</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -67358,17 +67358,17 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>143639</t>
+          <t>72206</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Sander</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Van Uytvanck</t>
+          <t>Varga</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -67380,12 +67380,12 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>72206</t>
+          <t>65110</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Katalin</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -67395,46 +67395,46 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>65110</t>
+          <t>147334</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Katalin</t>
+          <t>Hector</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Varga</t>
+          <t>Vazquez</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>147334</t>
+          <t>57980</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Hector</t>
+          <t>Pedro</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Vazquez</t>
+          <t>Vazquez Llenin</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -67446,61 +67446,61 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>57980</t>
+          <t>46844</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Pedro</t>
+          <t>Miriam</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Vazquez Llenin</t>
+          <t>Vega</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>46844</t>
+          <t>123334</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Miriam</t>
+          <t>Izan</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Vega</t>
+          <t>Velasco</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>123334</t>
+          <t>106218</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Izan</t>
+          <t>Sonu</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Velasco</t>
+          <t>Verma</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -67512,61 +67512,61 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>106218</t>
+          <t>100260</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Sonu</t>
+          <t>Nicci</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Verma</t>
+          <t>Vesely</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>100260</t>
+          <t>129703</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Nicci</t>
+          <t>Yann</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Vesely</t>
+          <t>Vilaca</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>129703</t>
+          <t>102756</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Yann</t>
+          <t>Pierre</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Vilaca</t>
+          <t>Vilella</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -67578,17 +67578,17 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>102756</t>
+          <t>128002</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Pierre</t>
+          <t>Matteo</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Vilella</t>
+          <t>Vittor</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -67600,17 +67600,17 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>128002</t>
+          <t>147168</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Matteo</t>
+          <t>Maksym</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Vittor</t>
+          <t>Vladychko</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -67622,39 +67622,39 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>147168</t>
+          <t>147275</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Maksym</t>
+          <t>Aleksandra</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Vladychko</t>
+          <t>Vlasova</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>147275</t>
+          <t>160667</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Aleksandra</t>
+          <t>Adela</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Vlasova</t>
+          <t>Vlckova</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -67666,39 +67666,39 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>160667</t>
+          <t>147774</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Adela</t>
+          <t>Keegan</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Vlckova</t>
+          <t>Vogt</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>147774</t>
+          <t>36743</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Keegan</t>
+          <t>Eivind</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Vogt</t>
+          <t>Vold</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -67710,12 +67710,12 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>36743</t>
+          <t>63310</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Eivind</t>
+          <t>Jon Amund</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -67732,39 +67732,39 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>63310</t>
+          <t>160156</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Jon Amund</t>
+          <t>Larisa</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Vold</t>
+          <t>Volik</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>160156</t>
+          <t>114992</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Larisa</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Volik</t>
+          <t>Voriskova</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -67776,61 +67776,61 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>114992</t>
+          <t>147270</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Karolina</t>
+          <t>Tymofii</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Voriskova</t>
+          <t>Vozniuk</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>147270</t>
+          <t>72106</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Tymofii</t>
+          <t>Emiri</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Vozniuk</t>
+          <t>Watanabe</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>72106</t>
+          <t>89206</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Emiri</t>
+          <t>Annette</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Watanabe</t>
+          <t>Wehrmann</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -67842,39 +67842,39 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>89206</t>
+          <t>102100</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Annette</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Wehrmann</t>
+          <t>White</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>102100</t>
+          <t>133170</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Wilga</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -67886,12 +67886,12 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>133170</t>
+          <t>113244</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Eryk</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -67908,105 +67908,105 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>113244</t>
+          <t>111725</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Eryk</t>
+          <t>Jade</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Wilga</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>111725</t>
+          <t>135807</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Jade</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Worgan</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>135807</t>
+          <t>159904</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Giselle Xiu Hui</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Worgan</t>
+          <t>Wu</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>159904</t>
+          <t>104900</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Giselle Xiu Hui</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Wu</t>
+          <t>Wydera</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>104900</t>
+          <t>133181</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Igor</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Wydera</t>
+          <t>Wyszkowski</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -68018,39 +68018,39 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>133181</t>
+          <t>131206</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Igor</t>
+          <t>Albina</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Wyszkowski</t>
+          <t>Yakobchuk</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>131206</t>
+          <t>147000</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Albina</t>
+          <t>Rion</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Yakobchuk</t>
+          <t>Yamaki</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -68062,17 +68062,17 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>147000</t>
+          <t>158986</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Rion</t>
+          <t>Haruna</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Yamaki</t>
+          <t>Yamamoto</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -68084,61 +68084,61 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>158986</t>
+          <t>122915</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Haruna</t>
+          <t>Dmytro</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Yamamoto</t>
+          <t>Yanchuk</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>122915</t>
+          <t>155124</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Dmytro</t>
+          <t>Yuxin</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Yanchuk</t>
+          <t>Yang</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>155124</t>
+          <t>161891</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Yuxin</t>
+          <t>Mariia</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Yang</t>
+          <t>Yankevych</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -68150,39 +68150,39 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>161891</t>
+          <t>153982</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Mariia</t>
+          <t>Serhii</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Yankevych</t>
+          <t>Yemelianov</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>153982</t>
+          <t>63473</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Serhii</t>
+          <t>Hamish</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Yemelianov</t>
+          <t>Young</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -68194,39 +68194,39 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>63473</t>
+          <t>155120</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Hamish</t>
+          <t>Jessie</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Young</t>
+          <t>Yu</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>155120</t>
+          <t>147311</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Jessie</t>
+          <t>Panka</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Yu</t>
+          <t>Zatyko</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -68238,61 +68238,61 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>147311</t>
+          <t>44574</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Panka</t>
+          <t>Jakub</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Zatyko</t>
+          <t>Zavrel</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>44574</t>
+          <t>161886</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Jakub</t>
+          <t>Yana</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Zavrel</t>
+          <t>Zhemir</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>161886</t>
+          <t>122962</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Yana</t>
+          <t>Tetiana</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Zhemir</t>
+          <t>Zozulia</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -68304,17 +68304,17 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>122962</t>
+          <t>132981</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Tetiana</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Zozulia</t>
+          <t>Zucca</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -68326,64 +68326,42 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>132981</t>
+          <t>49457</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Mateusz</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Zucca</t>
+          <t>Zuchora</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>49457</t>
+          <t>135239</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Giulio Maria</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Zuchora</t>
+          <t>Zugna</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>135239</t>
-        </is>
-      </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>Giulio Maria</t>
-        </is>
-      </c>
-      <c r="C476" t="inlineStr">
-        <is>
-          <t>Zugna</t>
-        </is>
-      </c>
-      <c r="D476" t="inlineStr">
         <is>
           <t>M</t>
         </is>

--- a/events/Gyor_2025_MAR/Gyor_2025_MAR_Results.xlsx
+++ b/events/Gyor_2025_MAR/Gyor_2025_MAR_Results.xlsx
@@ -551,7 +551,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -13571,7 +13571,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -13647,7 +13647,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -13723,7 +13723,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -13875,7 +13875,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -14027,7 +14027,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -14103,7 +14103,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -14179,7 +14179,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -14255,7 +14255,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -14331,7 +14331,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -16915,7 +16915,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -16991,7 +16991,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -17067,7 +17067,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -17143,7 +17143,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -17295,7 +17295,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -17371,7 +17371,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -17447,7 +17447,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -17599,7 +17599,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -17675,7 +17675,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -17827,7 +17827,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -17903,7 +17903,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -17979,7 +17979,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -18055,7 +18055,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -18207,7 +18207,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -18283,7 +18283,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -18359,7 +18359,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -18511,7 +18511,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -18587,7 +18587,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -18663,7 +18663,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -18739,7 +18739,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -18815,7 +18815,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -18891,7 +18891,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -18967,7 +18967,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -19043,7 +19043,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -19119,7 +19119,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -19195,7 +19195,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -19347,7 +19347,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -19423,7 +19423,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -19499,7 +19499,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -19575,7 +19575,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -19651,7 +19651,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -19727,7 +19727,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -19803,7 +19803,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -19879,7 +19879,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -25883,7 +25883,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -25959,7 +25959,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -26035,7 +26035,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -26111,7 +26111,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -26187,7 +26187,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -26263,7 +26263,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -26339,7 +26339,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -26415,7 +26415,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -26491,7 +26491,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -26567,7 +26567,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -26643,7 +26643,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -26719,7 +26719,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -26795,7 +26795,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -26871,7 +26871,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -26947,7 +26947,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -27023,7 +27023,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -27099,7 +27099,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -27175,7 +27175,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -27251,7 +27251,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -27327,7 +27327,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -27403,7 +27403,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -27479,7 +27479,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -27555,7 +27555,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -27631,7 +27631,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -27707,7 +27707,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -27783,7 +27783,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -27859,7 +27859,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -27935,7 +27935,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -28011,7 +28011,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -28087,7 +28087,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -28163,7 +28163,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -28239,7 +28239,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -28315,7 +28315,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -28391,7 +28391,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -28467,7 +28467,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -28543,7 +28543,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -28619,7 +28619,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -28695,7 +28695,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -28771,7 +28771,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -28847,7 +28847,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -28923,7 +28923,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -28999,7 +28999,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -29075,7 +29075,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -29151,7 +29151,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -29227,7 +29227,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -29303,7 +29303,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -29379,7 +29379,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -29455,7 +29455,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -29531,7 +29531,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -29607,7 +29607,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -29683,7 +29683,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -29759,7 +29759,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -29835,7 +29835,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -29911,7 +29911,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -29987,7 +29987,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -30063,7 +30063,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -30139,7 +30139,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -30215,7 +30215,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -30291,7 +30291,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -30367,7 +30367,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -30443,7 +30443,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -30519,7 +30519,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -33559,7 +33559,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -33635,7 +33635,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -33711,7 +33711,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -33787,7 +33787,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -33863,7 +33863,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -33939,7 +33939,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -34015,7 +34015,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -34091,7 +34091,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -34167,7 +34167,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -34319,7 +34319,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -34395,7 +34395,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -34471,7 +34471,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -34547,7 +34547,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -34623,7 +34623,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -34699,7 +34699,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -34775,7 +34775,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -34851,7 +34851,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -34927,7 +34927,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -35003,7 +35003,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -35079,7 +35079,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -35155,7 +35155,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -35231,7 +35231,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -35307,7 +35307,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -35383,7 +35383,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -35459,7 +35459,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -35535,7 +35535,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -35611,7 +35611,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -35687,7 +35687,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -35763,7 +35763,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -35839,7 +35839,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -35915,7 +35915,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -35991,7 +35991,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -36067,7 +36067,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -36143,7 +36143,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -36219,7 +36219,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -36295,7 +36295,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -36371,7 +36371,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -36447,7 +36447,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -36523,7 +36523,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -36599,7 +36599,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -36675,7 +36675,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -36751,7 +36751,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -36827,7 +36827,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -36903,7 +36903,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -36979,7 +36979,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -37055,7 +37055,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -37131,7 +37131,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -37207,7 +37207,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -37283,7 +37283,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -37359,7 +37359,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -37435,7 +37435,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -37511,7 +37511,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -37583,7 +37583,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -37659,7 +37659,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -37735,7 +37735,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -37811,7 +37811,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -37887,7 +37887,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -37963,7 +37963,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -38039,7 +38039,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -38115,7 +38115,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -38191,7 +38191,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -38267,7 +38267,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -38343,7 +38343,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -38419,7 +38419,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -38495,7 +38495,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -38571,7 +38571,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -38647,7 +38647,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -38723,7 +38723,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -38799,7 +38799,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -38875,7 +38875,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -38951,7 +38951,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -39027,7 +39027,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -39103,7 +39103,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -39179,7 +39179,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -39255,7 +39255,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -39331,7 +39331,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -39407,7 +39407,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -39483,7 +39483,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -39559,7 +39559,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -39635,7 +39635,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -39711,7 +39711,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -39787,7 +39787,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -39863,7 +39863,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -39939,7 +39939,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -40015,7 +40015,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -40091,7 +40091,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>U23</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -40167,7 +40167,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -40243,7 +40243,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -40319,7 +40319,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -40395,7 +40395,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -40471,7 +40471,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -40547,7 +40547,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -40623,7 +40623,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -40699,7 +40699,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -40775,7 +40775,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -40851,7 +40851,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -40927,7 +40927,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -41003,7 +41003,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -41079,7 +41079,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -41155,7 +41155,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -41231,7 +41231,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -41307,7 +41307,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -41383,7 +41383,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -41459,7 +41459,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -41535,7 +41535,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -41611,7 +41611,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -41687,7 +41687,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -41839,7 +41839,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -41915,7 +41915,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -41991,7 +41991,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -42063,7 +42063,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -42139,7 +42139,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -42215,7 +42215,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -42291,7 +42291,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -42367,7 +42367,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -42443,7 +42443,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -42519,7 +42519,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -42595,7 +42595,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -42671,7 +42671,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -42747,7 +42747,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -42823,7 +42823,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -42899,7 +42899,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
@@ -42975,7 +42975,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -43051,7 +43051,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
@@ -43131,7 +43131,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -43211,7 +43211,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -43291,7 +43291,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -43371,7 +43371,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -43451,7 +43451,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -43531,7 +43531,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
@@ -43611,7 +43611,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -43691,7 +43691,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
@@ -43771,7 +43771,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
@@ -43851,7 +43851,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -43931,7 +43931,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -44011,7 +44011,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -44091,7 +44091,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
@@ -44171,7 +44171,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
@@ -44251,7 +44251,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -44331,7 +44331,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
@@ -44411,7 +44411,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -44491,7 +44491,7 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
@@ -44571,7 +44571,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
@@ -44651,7 +44651,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
@@ -44731,7 +44731,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
@@ -44811,7 +44811,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -44891,7 +44891,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -44971,7 +44971,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -45051,7 +45051,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -45131,7 +45131,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -45211,7 +45211,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -45291,7 +45291,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -51831,7 +51831,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -51911,7 +51911,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -51991,7 +51991,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -52071,7 +52071,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -52151,7 +52151,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -52231,7 +52231,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -52311,7 +52311,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -52391,7 +52391,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -52471,7 +52471,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -52551,7 +52551,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -52631,7 +52631,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -52711,7 +52711,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -52791,7 +52791,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -52871,7 +52871,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -52951,7 +52951,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -53031,7 +53031,7 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -53111,7 +53111,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -53191,7 +53191,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -53271,7 +53271,7 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -53351,7 +53351,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -53431,7 +53431,7 @@
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -53511,7 +53511,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -53591,7 +53591,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -53671,7 +53671,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>SENIOR</t>
+          <t>JUNIOR</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">

--- a/events/Gyor_2025_MAR/Gyor_2025_MAR_Results.xlsx
+++ b/events/Gyor_2025_MAR/Gyor_2025_MAR_Results.xlsx
@@ -28400,7 +28400,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>18000</v>
+        <v>18100</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>18000</v>
+        <v>18100</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
@@ -28552,7 +28552,7 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>18000</v>
+        <v>18100</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
@@ -28628,7 +28628,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>18000</v>
+        <v>18100</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>18000</v>
+        <v>18100</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>18000</v>
+        <v>18100</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>18000</v>
+        <v>18100</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -28932,7 +28932,7 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>18000</v>
+        <v>18100</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
@@ -29008,7 +29008,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>18000</v>
+        <v>18100</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>18000</v>
+        <v>18100</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
@@ -29160,7 +29160,7 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>18000</v>
+        <v>18100</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
@@ -29236,7 +29236,7 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>18000</v>
+        <v>18100</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
@@ -29312,7 +29312,7 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>18000</v>
+        <v>18100</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>18000</v>
+        <v>18100</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
@@ -29464,7 +29464,7 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>18000</v>
+        <v>18100</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>18000</v>
+        <v>18100</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
